--- a/月ノルマ/月間週次実績表_2026年9月版.xlsx
+++ b/月ノルマ/月間週次実績表_2026年9月版.xlsx
@@ -881,7 +881,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>追加の修正依頼あり。9/9に看護部へ提出予定。</t>
+          <t>追加の修正依頼あり。9/9に看護部へ提出済み。</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>内容がOKであればシステムへ掲載予定。</t>
+          <t>9/16に看護部長のOKを取得し、iPadに入れて納品。承認サイン等は依頼があったら追加予定。</t>
         </is>
       </c>
     </row>

--- a/月ノルマ/月間週次実績表_2026年9月版.xlsx
+++ b/月ノルマ/月間週次実績表_2026年9月版.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>未完了なら10月へ持ち越し。</t>
+          <t>動画自体は完了。追加システムの依頼時は施行予定(Wi-Fiが通じたら施行予定)。</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>【依頼対応】9/29のSW会議当日、必要に応じてシステムの編集対応。</t>
+          <t>【依頼対応】9/29のSW会議当日、SWの内容をまとめたシステム化の依頼に対応(院内)。</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -1565,14 +1565,14 @@
         </is>
       </c>
       <c r="E34" s="11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F34" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>依頼がなければ工数は減る見込み。</t>
+          <t>当日依頼:SWの内容のまとまったシステム化(2時間)。</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E36" s="11" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>0</v>
